--- a/Result/Bearing_Result_30/Ranking_Bearing_30.xlsx
+++ b/Result/Bearing_Result_30/Ranking_Bearing_30.xlsx
@@ -664,184 +664,199 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.9195785356415969</v>
+        <v>0.9323684167201846</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8671141924940684</v>
+        <v>0.8769162891366019</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9888321876602767</v>
+        <v>0.9910383529207867</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9422323394098945</v>
+        <v>0.9555531549936971</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.643669433774823</v>
+        <v>162.0246917886503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.9245492001955351</v>
+        <v>0.9195785356415969</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8930401280394596</v>
+        <v>0.8671141924940684</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9912000624627479</v>
+        <v>0.9888321876602767</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9480168301377184</v>
+        <v>0.9422323394098945</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>294.6492060064749</v>
+        <v>1.643669433774823</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0.9275311618704333</v>
+        <v>0.9245492001955351</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.883446048866777</v>
+        <v>0.8930401280394596</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9914888366857193</v>
+        <v>0.9912000624627479</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9501602214017923</v>
+        <v>0.9480168301377184</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.536367555874396</v>
+        <v>294.6492060064749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.9327141595857229</v>
+        <v>0.9275311618704333</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8827565318106738</v>
+        <v>0.883446048866777</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9906250403882948</v>
+        <v>0.9914888366857193</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9544004762737446</v>
+        <v>0.9501602214017923</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>174.1421826856499</v>
+        <v>4.536367555874396</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.8971374243141053</v>
+        <v>0.9327141595857229</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9207820099881058</v>
+        <v>0.8827565318106738</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9894035203997635</v>
+        <v>0.9906250403882948</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9329888733668548</v>
+        <v>0.9544004762737446</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2425349042250441</v>
+        <v>174.1421826856499</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SMOM</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.9332154854916674</v>
+        <v>0.8971374243141053</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9060627349363102</v>
+        <v>0.9207820099881058</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9918284740610075</v>
+        <v>0.9894035203997635</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9551118033701046</v>
+        <v>0.9329888733668548</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>167.7914999185745</v>
+        <v>0.2425349042250441</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>SMOM</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.9236110105784321</v>
+        <v>0.9332154854916674</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9008369929876526</v>
+        <v>0.9060627349363102</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9907473446884656</v>
+        <v>0.9918284740610075</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9458600611196757</v>
+        <v>0.9551118033701046</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>331.1302451025496</v>
+        <v>167.7914999185745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SOUP</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.8934498398193924</v>
+        <v>0.9236110105784321</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9425032560256809</v>
+        <v>0.9008369929876526</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9929256705458422</v>
+        <v>0.9907473446884656</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9578037413196003</v>
+        <v>0.9458600611196757</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>25.00565107870043</v>
+        <v>331.1302451025496</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
-        </is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.8934498398193924</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.9425032560256809</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.9929256705458422</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.9578037413196003</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>25.00565107870043</v>
       </c>
     </row>
   </sheetData>
@@ -938,13 +953,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>5</v>
@@ -966,10 +981,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>4</v>
@@ -981,7 +996,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>6</v>
@@ -994,10 +1009,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
@@ -1009,10 +1024,10 @@
         <v>7</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1022,13 +1037,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -1050,13 +1065,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6</v>
@@ -1065,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1078,13 +1093,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
@@ -1093,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>10</v>
@@ -1106,16 +1121,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>9</v>
@@ -1130,213 +1145,213 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>OREM-M</t>
+          <t>MC-RBO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>12</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>QC-SMOTE</t>
+          <t>OREM-M</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>NROMM</t>
+          <t>QC-SMOTE</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>12</v>
-      </c>
       <c r="H12" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GLOS</t>
+          <t>NROMM</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>10.25</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="E13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>11</v>
-      </c>
       <c r="H13" s="6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>SOUP</t>
+          <t>GLOS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SHSampler</t>
+          <t>SOUP</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>16</v>
-      </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MDO</t>
+          <t>SHSampler</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>14</v>
+        <v>12.75</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>EB-SMOTE</t>
+          <t>MDO</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>16</v>
@@ -1348,14 +1363,35 @@
         <v>15</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO</t>
-        </is>
+          <t>EB-SMOTE</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1396,19 +1432,19 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>参与均值与排名的完整模型 16 个; 数据集覆盖不全未参与 1 个</t>
+          <t>本组 17 个模型均在全部 8 个数据集上跑出结果, 全部参与均值与排名</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>排除模型</t>
+          <t>失败单元</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MC-RBO: 要求 8 个数据集, 有效结果 7 个, 缺失 1 个 (1 个 bearing); 不参与均值与排名, 仅保留模型名</t>
+          <t>MC-RBO × IR30_Ottawa: 指标为 NaN/Error, 视为未跑出结果, 不参与聚合</t>
         </is>
       </c>
     </row>
